--- a/db/Profesor_materia.xlsx
+++ b/db/Profesor_materia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PosGrado\Proyecto Titulacion\Timetabling\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{240A86A4-B8E9-44FD-9E69-1AE67B50A835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9E1F8F1-262A-4376-AF56-9ADEEB28A690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{16EDC1B1-E885-4BAF-A840-B27AD8A443E7}"/>
+    <workbookView xWindow="1980" yWindow="4170" windowWidth="28785" windowHeight="15345" xr2:uid="{16EDC1B1-E885-4BAF-A840-B27AD8A443E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,12 +34,348 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="114">
   <si>
     <t>profesor_id</t>
   </si>
   <si>
     <t>materia_id</t>
+  </si>
+  <si>
+    <t>CI-IC-001</t>
+  </si>
+  <si>
+    <t>TC-IC-001</t>
+  </si>
+  <si>
+    <t>CA-IC-001</t>
+  </si>
+  <si>
+    <t>RT-IC-001</t>
+  </si>
+  <si>
+    <t>AM-IC-001</t>
+  </si>
+  <si>
+    <t>RT-IC-002</t>
+  </si>
+  <si>
+    <t>TC-IC-002</t>
+  </si>
+  <si>
+    <t>CA-IC-002</t>
+  </si>
+  <si>
+    <t>AM-IC-002</t>
+  </si>
+  <si>
+    <t>CI-IC-002</t>
+  </si>
+  <si>
+    <t>RT-IC-003</t>
+  </si>
+  <si>
+    <t>TC-IC-003</t>
+  </si>
+  <si>
+    <t>DI-IC-001</t>
+  </si>
+  <si>
+    <t>AM-IC-003</t>
+  </si>
+  <si>
+    <t>CI-IC-003</t>
+  </si>
+  <si>
+    <t>FD-IC-001</t>
+  </si>
+  <si>
+    <t>SR-INC-001</t>
+  </si>
+  <si>
+    <t>LEM-INC-001</t>
+  </si>
+  <si>
+    <t>FD-INC-001</t>
+  </si>
+  <si>
+    <t>TC-INC-001</t>
+  </si>
+  <si>
+    <t>AM-INC-001</t>
+  </si>
+  <si>
+    <t>DI-INC-001</t>
+  </si>
+  <si>
+    <t>PC-INC-001</t>
+  </si>
+  <si>
+    <t>INI-INC-001</t>
+  </si>
+  <si>
+    <t>SR-INC-002</t>
+  </si>
+  <si>
+    <t>LEM-INC-002</t>
+  </si>
+  <si>
+    <t>FD-INC-002</t>
+  </si>
+  <si>
+    <t>TC-INC-002</t>
+  </si>
+  <si>
+    <t>AM-INC-002</t>
+  </si>
+  <si>
+    <t>DI-INC-002</t>
+  </si>
+  <si>
+    <t>PC-INC-002</t>
+  </si>
+  <si>
+    <t>SR-INC-003</t>
+  </si>
+  <si>
+    <t>TM-INC-003</t>
+  </si>
+  <si>
+    <t>FD-INC-003</t>
+  </si>
+  <si>
+    <t>TC-INC-003</t>
+  </si>
+  <si>
+    <t>AMC-INC-003</t>
+  </si>
+  <si>
+    <t>DI-INC-003</t>
+  </si>
+  <si>
+    <t>PC-INC-003</t>
+  </si>
+  <si>
+    <t>SR-BC-001</t>
+  </si>
+  <si>
+    <t>TM-BC-001</t>
+  </si>
+  <si>
+    <t>DM-BC-001</t>
+  </si>
+  <si>
+    <t>AM-BC-001</t>
+  </si>
+  <si>
+    <t>CN-BC-001</t>
+  </si>
+  <si>
+    <t>OF-BC-001</t>
+  </si>
+  <si>
+    <t>SR-BC-002</t>
+  </si>
+  <si>
+    <t>TM-BC-002</t>
+  </si>
+  <si>
+    <t>DM-BC-002</t>
+  </si>
+  <si>
+    <t>AM-BC-002</t>
+  </si>
+  <si>
+    <t>CN-BC-002</t>
+  </si>
+  <si>
+    <t>OF-BC-002</t>
+  </si>
+  <si>
+    <t>SR-BC-003</t>
+  </si>
+  <si>
+    <t>TM-BC-003</t>
+  </si>
+  <si>
+    <t>DM-BC-003</t>
+  </si>
+  <si>
+    <t>ITV-BC-001</t>
+  </si>
+  <si>
+    <t>CN-BC-003</t>
+  </si>
+  <si>
+    <t>OF-BC-003</t>
+  </si>
+  <si>
+    <t>SR-ITC-001</t>
+  </si>
+  <si>
+    <t>TM-ITC-001</t>
+  </si>
+  <si>
+    <t>DIM-ITC-001</t>
+  </si>
+  <si>
+    <t>AMT-ITC-001</t>
+  </si>
+  <si>
+    <t>FD-ITC-001</t>
+  </si>
+  <si>
+    <t>TC-ITC-001</t>
+  </si>
+  <si>
+    <t>PC-ITC-001</t>
+  </si>
+  <si>
+    <t>INI-ITC-001</t>
+  </si>
+  <si>
+    <t>SR-ITC-002</t>
+  </si>
+  <si>
+    <t>TM-ITC-002</t>
+  </si>
+  <si>
+    <t>DM-ITC-002</t>
+  </si>
+  <si>
+    <t>FD-ITC-002</t>
+  </si>
+  <si>
+    <t>TC-ITC-002</t>
+  </si>
+  <si>
+    <t>CJ-ITC-001</t>
+  </si>
+  <si>
+    <t>OF-ITC-001</t>
+  </si>
+  <si>
+    <t>SR-ITC-003</t>
+  </si>
+  <si>
+    <t>TM-ITC-003</t>
+  </si>
+  <si>
+    <t>DM-ITC-003</t>
+  </si>
+  <si>
+    <t>FD-ITC-003</t>
+  </si>
+  <si>
+    <t>TC-ITC-003</t>
+  </si>
+  <si>
+    <t>CJ-ITC-002</t>
+  </si>
+  <si>
+    <t>OF-ITC-002</t>
+  </si>
+  <si>
+    <t>SR-IMC-001</t>
+  </si>
+  <si>
+    <t>DM-IMC-001</t>
+  </si>
+  <si>
+    <t>ARM-IMC-001</t>
+  </si>
+  <si>
+    <t>TV-IMC-001</t>
+  </si>
+  <si>
+    <t>HA-IMC-001</t>
+  </si>
+  <si>
+    <t>CJ-IMC-001</t>
+  </si>
+  <si>
+    <t>OF-IMC-001</t>
+  </si>
+  <si>
+    <t>SR-IMC-002</t>
+  </si>
+  <si>
+    <t>DM-IMC-002</t>
+  </si>
+  <si>
+    <t>ARM-IMC-002</t>
+  </si>
+  <si>
+    <t>ANM-IMC-001</t>
+  </si>
+  <si>
+    <t>HA-IMC-002</t>
+  </si>
+  <si>
+    <t>CJ-IMC-002</t>
+  </si>
+  <si>
+    <t>OF-IMC-002</t>
+  </si>
+  <si>
+    <t>SR-IMC-003</t>
+  </si>
+  <si>
+    <t>DM-IMC-003</t>
+  </si>
+  <si>
+    <t>AR-IMC-003</t>
+  </si>
+  <si>
+    <t>ANM-IMC-002</t>
+  </si>
+  <si>
+    <t>HM-IMC-001</t>
+  </si>
+  <si>
+    <t>CJ-IMC-003</t>
+  </si>
+  <si>
+    <t>OF-IMC-003</t>
+  </si>
+  <si>
+    <t>INC-OC</t>
+  </si>
+  <si>
+    <t>INC-OG</t>
+  </si>
+  <si>
+    <t>INC-FL</t>
+  </si>
+  <si>
+    <t>OCA</t>
+  </si>
+  <si>
+    <t>OGA</t>
+  </si>
+  <si>
+    <t>OVA</t>
+  </si>
+  <si>
+    <t>OPA</t>
+  </si>
+  <si>
+    <t>OCB</t>
+  </si>
+  <si>
+    <t>OGB</t>
+  </si>
+  <si>
+    <t>OVB</t>
+  </si>
+  <si>
+    <t>OPB</t>
+  </si>
+  <si>
+    <t>OS</t>
+  </si>
+  <si>
+    <t>NULL</t>
   </si>
 </sst>
 </file>
@@ -391,7 +727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{789EE592-4803-4FE8-90C7-40459AA7562F}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B151"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -402,6 +738,1206 @@
         <v>1</v>
       </c>
     </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1004</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1004</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1025</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1023</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1026</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1023</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1006</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1006</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1023</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1025</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1006</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1006</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1026</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1018</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1018</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>1014</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>1011</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1011</v>
+      </c>
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>1004</v>
+      </c>
+      <c r="B20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>1004</v>
+      </c>
+      <c r="B21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>1006</v>
+      </c>
+      <c r="B22" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>1006</v>
+      </c>
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>1018</v>
+      </c>
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>1018</v>
+      </c>
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>1019</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>1026</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>1011</v>
+      </c>
+      <c r="B28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>1018</v>
+      </c>
+      <c r="B29" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>1004</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>1004</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>1014</v>
+      </c>
+      <c r="B32" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>1014</v>
+      </c>
+      <c r="B33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>1002</v>
+      </c>
+      <c r="B34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>1002</v>
+      </c>
+      <c r="B35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>1016</v>
+      </c>
+      <c r="B36" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>1016</v>
+      </c>
+      <c r="B37" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>1014</v>
+      </c>
+      <c r="B38" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>1014</v>
+      </c>
+      <c r="B39" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>1001</v>
+      </c>
+      <c r="B40" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>1001</v>
+      </c>
+      <c r="B41" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>1007</v>
+      </c>
+      <c r="B42" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>1007</v>
+      </c>
+      <c r="B43" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>1022</v>
+      </c>
+      <c r="B44" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>1022</v>
+      </c>
+      <c r="B45" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>1009</v>
+      </c>
+      <c r="B46" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>1009</v>
+      </c>
+      <c r="B47" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>113</v>
+      </c>
+      <c r="B48" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>113</v>
+      </c>
+      <c r="B49" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>1002</v>
+      </c>
+      <c r="B50" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>1002</v>
+      </c>
+      <c r="B51" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>1011</v>
+      </c>
+      <c r="B52" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>1016</v>
+      </c>
+      <c r="B53" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>1014</v>
+      </c>
+      <c r="B54" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>1014</v>
+      </c>
+      <c r="B55" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>1001</v>
+      </c>
+      <c r="B56" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>1025</v>
+      </c>
+      <c r="B57" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>1007</v>
+      </c>
+      <c r="B58" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>1007</v>
+      </c>
+      <c r="B59" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>1010</v>
+      </c>
+      <c r="B60" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>1018</v>
+      </c>
+      <c r="B61" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>1009</v>
+      </c>
+      <c r="B62" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>1009</v>
+      </c>
+      <c r="B63" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>1012</v>
+      </c>
+      <c r="B64" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>1008</v>
+      </c>
+      <c r="B65" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>1025</v>
+      </c>
+      <c r="B66" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>1025</v>
+      </c>
+      <c r="B67" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>1007</v>
+      </c>
+      <c r="B68" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>1022</v>
+      </c>
+      <c r="B69" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>1009</v>
+      </c>
+      <c r="B70" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>1017</v>
+      </c>
+      <c r="B71" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>1016</v>
+      </c>
+      <c r="B72" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>1019</v>
+      </c>
+      <c r="B73" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>1019</v>
+      </c>
+      <c r="B74" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>1008</v>
+      </c>
+      <c r="B75" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>1010</v>
+      </c>
+      <c r="B76" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>1009</v>
+      </c>
+      <c r="B77" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>1008</v>
+      </c>
+      <c r="B78" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>1027</v>
+      </c>
+      <c r="B79" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>1007</v>
+      </c>
+      <c r="B80" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>1008</v>
+      </c>
+      <c r="B81" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>1010</v>
+      </c>
+      <c r="B82" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>1026</v>
+      </c>
+      <c r="B83" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>1024</v>
+      </c>
+      <c r="B84" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>1027</v>
+      </c>
+      <c r="B85" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>1015</v>
+      </c>
+      <c r="B86" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>1008</v>
+      </c>
+      <c r="B87" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>1010</v>
+      </c>
+      <c r="B88" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>1002</v>
+      </c>
+      <c r="B89" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>1019</v>
+      </c>
+      <c r="B90" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>1016</v>
+      </c>
+      <c r="B91" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>1011</v>
+      </c>
+      <c r="B92" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>1005</v>
+      </c>
+      <c r="B93" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>1010</v>
+      </c>
+      <c r="B94" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>1010</v>
+      </c>
+      <c r="B95" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>1011</v>
+      </c>
+      <c r="B96" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>1010</v>
+      </c>
+      <c r="B97" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>1010</v>
+      </c>
+      <c r="B98" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>1001</v>
+      </c>
+      <c r="B99" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>1001</v>
+      </c>
+      <c r="B100" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>1015</v>
+      </c>
+      <c r="B101" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>1015</v>
+      </c>
+      <c r="B102" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>113</v>
+      </c>
+      <c r="B103" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>113</v>
+      </c>
+      <c r="B104" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>1020</v>
+      </c>
+      <c r="B105" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>1011</v>
+      </c>
+      <c r="B106" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>1024</v>
+      </c>
+      <c r="B107" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>1003</v>
+      </c>
+      <c r="B108" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>1025</v>
+      </c>
+      <c r="B109" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>1001</v>
+      </c>
+      <c r="B110" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>1001</v>
+      </c>
+      <c r="B111" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>1028</v>
+      </c>
+      <c r="B112" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>1011</v>
+      </c>
+      <c r="B113" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>1028</v>
+      </c>
+      <c r="B114" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>1014</v>
+      </c>
+      <c r="B115" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>1025</v>
+      </c>
+      <c r="B116" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>1001</v>
+      </c>
+      <c r="B117" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>1001</v>
+      </c>
+      <c r="B118" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>1022</v>
+      </c>
+      <c r="B119" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>1015</v>
+      </c>
+      <c r="B120" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>1013</v>
+      </c>
+      <c r="B121" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>1015</v>
+      </c>
+      <c r="B122" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>1013</v>
+      </c>
+      <c r="B123" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>1001</v>
+      </c>
+      <c r="B124" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>1001</v>
+      </c>
+      <c r="B125" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>1008</v>
+      </c>
+      <c r="B126" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>1018</v>
+      </c>
+      <c r="B127" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>1007</v>
+      </c>
+      <c r="B128" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>1027</v>
+      </c>
+      <c r="B129" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>1007</v>
+      </c>
+      <c r="B130" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>1001</v>
+      </c>
+      <c r="B131" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>1001</v>
+      </c>
+      <c r="B132" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>1008</v>
+      </c>
+      <c r="B133" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>1023</v>
+      </c>
+      <c r="B134" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>1024</v>
+      </c>
+      <c r="B135" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>1027</v>
+      </c>
+      <c r="B136" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>1007</v>
+      </c>
+      <c r="B137" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>1001</v>
+      </c>
+      <c r="B138" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>1001</v>
+      </c>
+      <c r="B139" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>1016</v>
+      </c>
+      <c r="B140" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>1007</v>
+      </c>
+      <c r="B141" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>1002</v>
+      </c>
+      <c r="B142" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>1001</v>
+      </c>
+      <c r="B143" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>1009</v>
+      </c>
+      <c r="B144" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>1005</v>
+      </c>
+      <c r="B145" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>1021</v>
+      </c>
+      <c r="B146" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>1017</v>
+      </c>
+      <c r="B147" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>1002</v>
+      </c>
+      <c r="B148" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>1013</v>
+      </c>
+      <c r="B149" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>1021</v>
+      </c>
+      <c r="B150" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>1017</v>
+      </c>
+      <c r="B151" t="s">
+        <v>112</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
